--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224126</v>
+        <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>78793</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R3" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224125</v>
+        <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R4" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224128</v>
+        <v>129224126</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224125</v>
+        <v>129224128</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R3" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224126</v>
+        <v>129224125</v>
       </c>
       <c r="B4" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R4" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224126</v>
+        <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R3" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224125</v>
+        <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R4" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R2" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224125</v>
+        <v>129224128</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R3" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224125</v>
+        <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R2" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R3" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224128</v>
+        <v>129224126</v>
       </c>
       <c r="B2" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224125</v>
+        <v>129224128</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R3" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224126</v>
+        <v>129224125</v>
       </c>
       <c r="B4" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R4" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224126</v>
+        <v>129224128</v>
       </c>
       <c r="B2" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R3" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224125</v>
+        <v>129224126</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R4" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B2" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R2" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224125</v>
+        <v>129224128</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R3" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224128</v>
+        <v>129224126</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224126</v>
+        <v>129224128</v>
       </c>
       <c r="B4" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 51227-2025 artfynd.xlsx
+++ b/artfynd/A 51227-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224125</v>
+        <v>129224126</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511657</v>
+        <v>511656</v>
       </c>
       <c r="R2" t="n">
-        <v>6792753</v>
+        <v>6792754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224126</v>
+        <v>129224128</v>
       </c>
       <c r="B3" t="n">
-        <v>78802</v>
+        <v>79689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224128</v>
+        <v>129224125</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>78827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511656</v>
+        <v>511657</v>
       </c>
       <c r="R4" t="n">
-        <v>6792754</v>
+        <v>6792753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
